--- a/v2/uploads/diccionario/CLACOS.xlsx
+++ b/v2/uploads/diccionario/CLACOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aminerals.sharepoint.com/sites/Gcia.PlanificacinyControldeGestin/Documentos compartidos/Disco Gestión/01 Control de Gestión/01 Reporting/06 Reporte gestión/2026/05-2026/06 Actividad Corporativa y Exploraciones/Power BI/BASES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amsmmadrida\Repositorios Personales Control Gestion\amsa-budget-corporativo\v2\uploads\diccionario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="940" documentId="14_{96E76416-166F-4F24-BF8B-27ADF6C83D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D3F1552-4CB2-4551-8DFB-3C320A6F5896}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA66CEF-099B-477A-AEC6-61FD4C7BD8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GP_CO2P" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12291" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12339" uniqueCount="749">
   <si>
     <t>Cód_Agrupación1</t>
   </si>
@@ -3214,19 +3214,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:H445"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" customWidth="1"/>
-    <col min="2" max="2" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -3902,7 +3902,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>8</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -4162,7 +4162,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -4500,7 +4500,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>8</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>8</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>8</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -4890,7 +4890,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>8</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -5020,7 +5020,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -5046,7 +5046,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>8</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>8</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -5150,7 +5150,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -5202,7 +5202,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -5306,7 +5306,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -5462,7 +5462,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>8</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -5514,7 +5514,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>8</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>8</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>8</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -5670,7 +5670,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -5696,7 +5696,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>8</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -5748,7 +5748,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>8</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -5904,7 +5904,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>8</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>8</v>
       </c>
@@ -5956,7 +5956,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>8</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>8</v>
       </c>
@@ -6060,7 +6060,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>8</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>8</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>8</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -6190,7 +6190,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>8</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>8</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>8</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>8</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>8</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>8</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>8</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>8</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>8</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>8</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>8</v>
       </c>
@@ -6528,7 +6528,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>8</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>8</v>
       </c>
@@ -6580,7 +6580,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>8</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>8</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>8</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>8</v>
       </c>
@@ -6736,7 +6736,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>8</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>8</v>
       </c>
@@ -6788,7 +6788,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>8</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>8</v>
       </c>
@@ -6866,7 +6866,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>8</v>
       </c>
@@ -6918,7 +6918,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>8</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>8</v>
       </c>
@@ -6970,7 +6970,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>8</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>8</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>8</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>8</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>8</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>8</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>8</v>
       </c>
@@ -7152,7 +7152,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>8</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>8</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>8</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>8</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>8</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>8</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>8</v>
       </c>
@@ -7334,7 +7334,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>8</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>8</v>
       </c>
@@ -7386,7 +7386,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>8</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>8</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>8</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>8</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>8</v>
       </c>
@@ -7516,7 +7516,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>8</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>8</v>
       </c>
@@ -7568,7 +7568,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>8</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>8</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>8</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>8</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>8</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>8</v>
       </c>
@@ -7724,7 +7724,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>8</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>8</v>
       </c>
@@ -7776,7 +7776,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>8</v>
       </c>
@@ -7802,7 +7802,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>8</v>
       </c>
@@ -7828,7 +7828,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>8</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>8</v>
       </c>
@@ -7880,7 +7880,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>8</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>8</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>8</v>
       </c>
@@ -7958,7 +7958,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>8</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>8</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>8</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>8</v>
       </c>
@@ -8062,7 +8062,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>8</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>8</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>8</v>
       </c>
@@ -8140,7 +8140,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>8</v>
       </c>
@@ -8166,7 +8166,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>8</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>8</v>
       </c>
@@ -8218,7 +8218,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>8</v>
       </c>
@@ -8244,7 +8244,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>8</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>8</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>8</v>
       </c>
@@ -8322,7 +8322,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>8</v>
       </c>
@@ -8348,7 +8348,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>8</v>
       </c>
@@ -8374,7 +8374,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>8</v>
       </c>
@@ -8400,7 +8400,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>8</v>
       </c>
@@ -8426,7 +8426,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>8</v>
       </c>
@@ -8452,7 +8452,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>8</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>8</v>
       </c>
@@ -8504,7 +8504,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>8</v>
       </c>
@@ -8530,7 +8530,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>8</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>8</v>
       </c>
@@ -8582,7 +8582,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>8</v>
       </c>
@@ -8608,7 +8608,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>8</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>8</v>
       </c>
@@ -8660,7 +8660,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>8</v>
       </c>
@@ -8686,7 +8686,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>8</v>
       </c>
@@ -8712,7 +8712,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>8</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>8</v>
       </c>
@@ -8764,7 +8764,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>8</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>8</v>
       </c>
@@ -8816,7 +8816,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>8</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>8</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>8</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>8</v>
       </c>
@@ -8920,7 +8920,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>8</v>
       </c>
@@ -8946,7 +8946,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>8</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>8</v>
       </c>
@@ -8998,7 +8998,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>8</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>8</v>
       </c>
@@ -9050,7 +9050,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>8</v>
       </c>
@@ -9076,7 +9076,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>8</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>8</v>
       </c>
@@ -9128,7 +9128,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>8</v>
       </c>
@@ -9154,7 +9154,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>8</v>
       </c>
@@ -9180,7 +9180,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>8</v>
       </c>
@@ -9206,7 +9206,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>8</v>
       </c>
@@ -9232,7 +9232,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>8</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>8</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>8</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>8</v>
       </c>
@@ -9336,7 +9336,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>8</v>
       </c>
@@ -9362,7 +9362,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>8</v>
       </c>
@@ -9388,7 +9388,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>8</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>8</v>
       </c>
@@ -9440,7 +9440,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>8</v>
       </c>
@@ -9466,7 +9466,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>8</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>8</v>
       </c>
@@ -9518,7 +9518,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>8</v>
       </c>
@@ -9544,7 +9544,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>8</v>
       </c>
@@ -9570,7 +9570,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>8</v>
       </c>
@@ -9596,7 +9596,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>8</v>
       </c>
@@ -9622,7 +9622,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>8</v>
       </c>
@@ -9648,7 +9648,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>8</v>
       </c>
@@ -9674,7 +9674,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>8</v>
       </c>
@@ -9700,7 +9700,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>8</v>
       </c>
@@ -9726,7 +9726,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>8</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>8</v>
       </c>
@@ -9778,7 +9778,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>8</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>8</v>
       </c>
@@ -9830,7 +9830,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>8</v>
       </c>
@@ -9856,7 +9856,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>8</v>
       </c>
@@ -9882,7 +9882,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>8</v>
       </c>
@@ -9908,7 +9908,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>8</v>
       </c>
@@ -9934,7 +9934,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>8</v>
       </c>
@@ -9960,7 +9960,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>8</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>8</v>
       </c>
@@ -10012,7 +10012,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>8</v>
       </c>
@@ -10038,7 +10038,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>8</v>
       </c>
@@ -10064,7 +10064,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>8</v>
       </c>
@@ -10090,7 +10090,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>8</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>8</v>
       </c>
@@ -10142,7 +10142,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>8</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>8</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>8</v>
       </c>
@@ -10220,7 +10220,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>8</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>8</v>
       </c>
@@ -10272,7 +10272,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>8</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>8</v>
       </c>
@@ -10324,7 +10324,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>8</v>
       </c>
@@ -10350,7 +10350,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>8</v>
       </c>
@@ -10376,7 +10376,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>8</v>
       </c>
@@ -10402,7 +10402,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>8</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>8</v>
       </c>
@@ -10454,7 +10454,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>8</v>
       </c>
@@ -10480,7 +10480,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>8</v>
       </c>
@@ -10506,7 +10506,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>8</v>
       </c>
@@ -10532,7 +10532,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>8</v>
       </c>
@@ -10558,7 +10558,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>8</v>
       </c>
@@ -10584,7 +10584,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>8</v>
       </c>
@@ -10610,7 +10610,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>8</v>
       </c>
@@ -10636,7 +10636,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>8</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>8</v>
       </c>
@@ -10688,7 +10688,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>8</v>
       </c>
@@ -10714,7 +10714,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>8</v>
       </c>
@@ -10740,7 +10740,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>8</v>
       </c>
@@ -10766,7 +10766,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>8</v>
       </c>
@@ -10792,7 +10792,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>8</v>
       </c>
@@ -10818,7 +10818,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>8</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>8</v>
       </c>
@@ -10870,7 +10870,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>8</v>
       </c>
@@ -10896,7 +10896,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>8</v>
       </c>
@@ -10922,7 +10922,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>8</v>
       </c>
@@ -10948,7 +10948,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>8</v>
       </c>
@@ -10974,7 +10974,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>8</v>
       </c>
@@ -11000,7 +11000,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>8</v>
       </c>
@@ -11026,7 +11026,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>8</v>
       </c>
@@ -11052,7 +11052,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>8</v>
       </c>
@@ -11078,7 +11078,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>8</v>
       </c>
@@ -11104,7 +11104,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>8</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>8</v>
       </c>
@@ -11156,7 +11156,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>8</v>
       </c>
@@ -11182,7 +11182,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>8</v>
       </c>
@@ -11208,7 +11208,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>8</v>
       </c>
@@ -11234,7 +11234,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>8</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>8</v>
       </c>
@@ -11286,7 +11286,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>8</v>
       </c>
@@ -11312,7 +11312,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>8</v>
       </c>
@@ -11338,7 +11338,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>8</v>
       </c>
@@ -11364,7 +11364,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>8</v>
       </c>
@@ -11390,7 +11390,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>8</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>8</v>
       </c>
@@ -11442,7 +11442,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>8</v>
       </c>
@@ -11468,7 +11468,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>8</v>
       </c>
@@ -11494,7 +11494,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>8</v>
       </c>
@@ -11520,7 +11520,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>8</v>
       </c>
@@ -11546,7 +11546,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>8</v>
       </c>
@@ -11572,7 +11572,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>8</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>8</v>
       </c>
@@ -11624,7 +11624,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>8</v>
       </c>
@@ -11650,7 +11650,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>8</v>
       </c>
@@ -11676,7 +11676,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>8</v>
       </c>
@@ -11702,7 +11702,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>8</v>
       </c>
@@ -11728,7 +11728,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>8</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>8</v>
       </c>
@@ -11780,7 +11780,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>8</v>
       </c>
@@ -11806,7 +11806,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>8</v>
       </c>
@@ -11832,7 +11832,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>8</v>
       </c>
@@ -11858,7 +11858,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>8</v>
       </c>
@@ -11884,7 +11884,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>8</v>
       </c>
@@ -11910,7 +11910,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>8</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>8</v>
       </c>
@@ -11962,7 +11962,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>8</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>8</v>
       </c>
@@ -12014,7 +12014,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>8</v>
       </c>
@@ -12040,7 +12040,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>8</v>
       </c>
@@ -12066,7 +12066,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>8</v>
       </c>
@@ -12092,7 +12092,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>8</v>
       </c>
@@ -12118,7 +12118,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>8</v>
       </c>
@@ -12144,7 +12144,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>8</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>8</v>
       </c>
@@ -12196,7 +12196,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>8</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>8</v>
       </c>
@@ -12248,7 +12248,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>8</v>
       </c>
@@ -12274,7 +12274,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>8</v>
       </c>
@@ -12300,7 +12300,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>8</v>
       </c>
@@ -12326,7 +12326,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>8</v>
       </c>
@@ -12352,7 +12352,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>8</v>
       </c>
@@ -12378,7 +12378,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>8</v>
       </c>
@@ -12404,7 +12404,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>8</v>
       </c>
@@ -12430,7 +12430,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>8</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>8</v>
       </c>
@@ -12482,7 +12482,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>8</v>
       </c>
@@ -12508,7 +12508,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>8</v>
       </c>
@@ -12534,7 +12534,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>8</v>
       </c>
@@ -12560,7 +12560,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>8</v>
       </c>
@@ -12586,7 +12586,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>8</v>
       </c>
@@ -12612,7 +12612,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>8</v>
       </c>
@@ -12638,7 +12638,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>8</v>
       </c>
@@ -12664,7 +12664,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>8</v>
       </c>
@@ -12690,7 +12690,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>8</v>
       </c>
@@ -12716,7 +12716,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>8</v>
       </c>
@@ -12742,7 +12742,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>8</v>
       </c>
@@ -12768,7 +12768,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>8</v>
       </c>
@@ -12794,7 +12794,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>8</v>
       </c>
@@ -12820,7 +12820,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>8</v>
       </c>
@@ -12846,7 +12846,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>8</v>
       </c>
@@ -12872,7 +12872,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>8</v>
       </c>
@@ -12898,7 +12898,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>8</v>
       </c>
@@ -12924,7 +12924,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>8</v>
       </c>
@@ -12950,7 +12950,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>8</v>
       </c>
@@ -12976,7 +12976,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>8</v>
       </c>
@@ -13002,7 +13002,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>8</v>
       </c>
@@ -13028,7 +13028,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>8</v>
       </c>
@@ -13054,7 +13054,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>8</v>
       </c>
@@ -13080,7 +13080,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>8</v>
       </c>
@@ -13106,7 +13106,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>8</v>
       </c>
@@ -13132,7 +13132,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>8</v>
       </c>
@@ -13158,7 +13158,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>8</v>
       </c>
@@ -13184,7 +13184,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>8</v>
       </c>
@@ -13210,7 +13210,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>8</v>
       </c>
@@ -13236,7 +13236,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>8</v>
       </c>
@@ -13262,7 +13262,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>8</v>
       </c>
@@ -13288,7 +13288,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>8</v>
       </c>
@@ -13314,7 +13314,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>8</v>
       </c>
@@ -13340,7 +13340,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>8</v>
       </c>
@@ -13366,7 +13366,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>8</v>
       </c>
@@ -13392,7 +13392,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>8</v>
       </c>
@@ -13418,7 +13418,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>8</v>
       </c>
@@ -13444,7 +13444,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>8</v>
       </c>
@@ -13470,7 +13470,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>8</v>
       </c>
@@ -13496,7 +13496,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>8</v>
       </c>
@@ -13522,7 +13522,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>8</v>
       </c>
@@ -13548,7 +13548,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>8</v>
       </c>
@@ -13574,7 +13574,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>8</v>
       </c>
@@ -13600,7 +13600,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>8</v>
       </c>
@@ -13626,7 +13626,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>8</v>
       </c>
@@ -13652,7 +13652,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>8</v>
       </c>
@@ -13678,7 +13678,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>8</v>
       </c>
@@ -13704,7 +13704,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>8</v>
       </c>
@@ -13730,7 +13730,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>8</v>
       </c>
@@ -13756,7 +13756,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>8</v>
       </c>
@@ -13782,7 +13782,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>8</v>
       </c>
@@ -13808,7 +13808,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>8</v>
       </c>
@@ -13834,7 +13834,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>8</v>
       </c>
@@ -13860,7 +13860,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>8</v>
       </c>
@@ -13886,7 +13886,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>8</v>
       </c>
@@ -13912,7 +13912,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>8</v>
       </c>
@@ -13938,7 +13938,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>8</v>
       </c>
@@ -13964,7 +13964,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>8</v>
       </c>
@@ -13990,7 +13990,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>8</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>8</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>8</v>
       </c>
@@ -14068,7 +14068,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>8</v>
       </c>
@@ -14094,7 +14094,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>8</v>
       </c>
@@ -14120,7 +14120,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>8</v>
       </c>
@@ -14146,7 +14146,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>8</v>
       </c>
@@ -14172,7 +14172,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>8</v>
       </c>
@@ -14198,7 +14198,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>8</v>
       </c>
@@ -14224,7 +14224,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>8</v>
       </c>
@@ -14250,7 +14250,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>8</v>
       </c>
@@ -14276,7 +14276,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>8</v>
       </c>
@@ -14302,7 +14302,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>8</v>
       </c>
@@ -14328,7 +14328,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>8</v>
       </c>
@@ -14354,7 +14354,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>8</v>
       </c>
@@ -14380,7 +14380,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>8</v>
       </c>
@@ -14406,7 +14406,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>8</v>
       </c>
@@ -14432,7 +14432,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>8</v>
       </c>
@@ -14458,7 +14458,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>8</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>8</v>
       </c>
@@ -14510,7 +14510,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>8</v>
       </c>
@@ -14536,7 +14536,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>8</v>
       </c>
@@ -14562,7 +14562,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>8</v>
       </c>
@@ -14588,7 +14588,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>8</v>
       </c>
@@ -14614,7 +14614,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>8</v>
       </c>
@@ -14640,7 +14640,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>8</v>
       </c>
@@ -14666,7 +14666,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>8</v>
       </c>
@@ -14692,7 +14692,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>8</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>8</v>
       </c>
@@ -14744,7 +14744,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>8</v>
       </c>
@@ -14770,7 +14770,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>8</v>
       </c>
@@ -14806,32 +14806,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:T599"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T602"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="35.7109375" customWidth="1"/>
-    <col min="17" max="17" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
+    <col min="9" max="9" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.88671875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="35.6640625" customWidth="1"/>
+    <col min="17" max="17" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.88671875" customWidth="1"/>
+    <col min="19" max="19" width="15.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14893,7 +14893,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>529</v>
       </c>
@@ -14955,7 +14955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>529</v>
       </c>
@@ -15017,7 +15017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>529</v>
       </c>
@@ -15079,7 +15079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>529</v>
       </c>
@@ -15141,7 +15141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>529</v>
       </c>
@@ -15203,7 +15203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>529</v>
       </c>
@@ -15265,7 +15265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>529</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>529</v>
       </c>
@@ -15389,7 +15389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>529</v>
       </c>
@@ -15451,7 +15451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>529</v>
       </c>
@@ -15513,7 +15513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>529</v>
       </c>
@@ -15575,7 +15575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>529</v>
       </c>
@@ -15637,7 +15637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>529</v>
       </c>
@@ -15699,7 +15699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>529</v>
       </c>
@@ -15761,7 +15761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>529</v>
       </c>
@@ -15823,7 +15823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>529</v>
       </c>
@@ -15885,7 +15885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>529</v>
       </c>
@@ -15947,7 +15947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>529</v>
       </c>
@@ -16009,7 +16009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>529</v>
       </c>
@@ -16071,7 +16071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>529</v>
       </c>
@@ -16133,7 +16133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>529</v>
       </c>
@@ -16195,7 +16195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>529</v>
       </c>
@@ -16257,7 +16257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>529</v>
       </c>
@@ -16319,7 +16319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>529</v>
       </c>
@@ -16381,7 +16381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>529</v>
       </c>
@@ -16443,7 +16443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>529</v>
       </c>
@@ -16505,7 +16505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>529</v>
       </c>
@@ -16567,7 +16567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>529</v>
       </c>
@@ -16629,7 +16629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>529</v>
       </c>
@@ -16691,7 +16691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>529</v>
       </c>
@@ -16753,7 +16753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>529</v>
       </c>
@@ -16815,7 +16815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>529</v>
       </c>
@@ -16877,7 +16877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>529</v>
       </c>
@@ -16939,7 +16939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>529</v>
       </c>
@@ -17001,7 +17001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>529</v>
       </c>
@@ -17063,7 +17063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>529</v>
       </c>
@@ -17125,7 +17125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>529</v>
       </c>
@@ -17187,7 +17187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>529</v>
       </c>
@@ -17249,7 +17249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>529</v>
       </c>
@@ -17311,7 +17311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>529</v>
       </c>
@@ -17373,7 +17373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>529</v>
       </c>
@@ -17435,7 +17435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>529</v>
       </c>
@@ -17497,7 +17497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>529</v>
       </c>
@@ -17559,7 +17559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>529</v>
       </c>
@@ -17621,7 +17621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>529</v>
       </c>
@@ -17683,7 +17683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>529</v>
       </c>
@@ -17745,7 +17745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>529</v>
       </c>
@@ -17807,7 +17807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>529</v>
       </c>
@@ -17869,7 +17869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>529</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>529</v>
       </c>
@@ -17993,7 +17993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>529</v>
       </c>
@@ -18055,7 +18055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>529</v>
       </c>
@@ -18117,7 +18117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>529</v>
       </c>
@@ -18179,7 +18179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>529</v>
       </c>
@@ -18241,7 +18241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>529</v>
       </c>
@@ -18303,7 +18303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>529</v>
       </c>
@@ -18365,7 +18365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>529</v>
       </c>
@@ -18427,7 +18427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>529</v>
       </c>
@@ -18489,7 +18489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>529</v>
       </c>
@@ -18551,7 +18551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>529</v>
       </c>
@@ -18613,7 +18613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>529</v>
       </c>
@@ -18675,7 +18675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>529</v>
       </c>
@@ -18737,7 +18737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>529</v>
       </c>
@@ -18799,7 +18799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>529</v>
       </c>
@@ -18861,7 +18861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>529</v>
       </c>
@@ -18923,7 +18923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>529</v>
       </c>
@@ -18985,7 +18985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>529</v>
       </c>
@@ -19047,7 +19047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>529</v>
       </c>
@@ -19109,7 +19109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>529</v>
       </c>
@@ -19171,7 +19171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>529</v>
       </c>
@@ -19233,7 +19233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>529</v>
       </c>
@@ -19295,7 +19295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>529</v>
       </c>
@@ -19357,7 +19357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>529</v>
       </c>
@@ -19419,7 +19419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>529</v>
       </c>
@@ -19481,7 +19481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>529</v>
       </c>
@@ -19543,7 +19543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>529</v>
       </c>
@@ -19605,7 +19605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>529</v>
       </c>
@@ -19667,7 +19667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>529</v>
       </c>
@@ -19729,7 +19729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>529</v>
       </c>
@@ -19791,7 +19791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>529</v>
       </c>
@@ -19853,7 +19853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>529</v>
       </c>
@@ -19915,7 +19915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>529</v>
       </c>
@@ -19977,7 +19977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>529</v>
       </c>
@@ -20039,7 +20039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>529</v>
       </c>
@@ -20101,7 +20101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>529</v>
       </c>
@@ -20163,7 +20163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>529</v>
       </c>
@@ -20225,7 +20225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>529</v>
       </c>
@@ -20287,7 +20287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>529</v>
       </c>
@@ -20349,7 +20349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>529</v>
       </c>
@@ -20411,7 +20411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>529</v>
       </c>
@@ -20473,7 +20473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>529</v>
       </c>
@@ -20535,7 +20535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>529</v>
       </c>
@@ -20597,7 +20597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>529</v>
       </c>
@@ -20659,7 +20659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>529</v>
       </c>
@@ -20721,7 +20721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>529</v>
       </c>
@@ -20783,7 +20783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>529</v>
       </c>
@@ -20845,7 +20845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>529</v>
       </c>
@@ -20907,7 +20907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>529</v>
       </c>
@@ -20969,7 +20969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>529</v>
       </c>
@@ -21031,7 +21031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>529</v>
       </c>
@@ -21093,7 +21093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>529</v>
       </c>
@@ -21155,7 +21155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>529</v>
       </c>
@@ -21217,7 +21217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>529</v>
       </c>
@@ -21279,7 +21279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>529</v>
       </c>
@@ -21341,7 +21341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>529</v>
       </c>
@@ -21403,7 +21403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>529</v>
       </c>
@@ -21465,7 +21465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>529</v>
       </c>
@@ -21527,7 +21527,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>529</v>
       </c>
@@ -21589,7 +21589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>529</v>
       </c>
@@ -21651,7 +21651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>529</v>
       </c>
@@ -21713,7 +21713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>529</v>
       </c>
@@ -21775,7 +21775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>529</v>
       </c>
@@ -21837,7 +21837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>529</v>
       </c>
@@ -21899,7 +21899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>529</v>
       </c>
@@ -21961,7 +21961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>529</v>
       </c>
@@ -22023,7 +22023,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>529</v>
       </c>
@@ -22085,7 +22085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>529</v>
       </c>
@@ -22147,7 +22147,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>529</v>
       </c>
@@ -22209,7 +22209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>529</v>
       </c>
@@ -22271,7 +22271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>529</v>
       </c>
@@ -22333,7 +22333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>529</v>
       </c>
@@ -22395,7 +22395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>529</v>
       </c>
@@ -22457,7 +22457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>529</v>
       </c>
@@ -22519,7 +22519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>529</v>
       </c>
@@ -22581,7 +22581,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>529</v>
       </c>
@@ -22643,7 +22643,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>529</v>
       </c>
@@ -22705,7 +22705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>529</v>
       </c>
@@ -22767,7 +22767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>529</v>
       </c>
@@ -22829,7 +22829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>529</v>
       </c>
@@ -22891,7 +22891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>529</v>
       </c>
@@ -22953,7 +22953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>529</v>
       </c>
@@ -23015,7 +23015,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>529</v>
       </c>
@@ -23077,7 +23077,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>529</v>
       </c>
@@ -23139,7 +23139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>529</v>
       </c>
@@ -23201,7 +23201,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>529</v>
       </c>
@@ -23263,7 +23263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>529</v>
       </c>
@@ -23325,7 +23325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>529</v>
       </c>
@@ -23387,7 +23387,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>529</v>
       </c>
@@ -23449,7 +23449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>529</v>
       </c>
@@ -23511,7 +23511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>529</v>
       </c>
@@ -23573,7 +23573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>529</v>
       </c>
@@ -23635,7 +23635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>529</v>
       </c>
@@ -23697,7 +23697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>529</v>
       </c>
@@ -23759,7 +23759,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>529</v>
       </c>
@@ -23821,7 +23821,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>529</v>
       </c>
@@ -23883,7 +23883,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>529</v>
       </c>
@@ -23945,7 +23945,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>529</v>
       </c>
@@ -24007,7 +24007,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>529</v>
       </c>
@@ -24069,7 +24069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>529</v>
       </c>
@@ -24131,7 +24131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>529</v>
       </c>
@@ -24193,7 +24193,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>529</v>
       </c>
@@ -24255,7 +24255,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>529</v>
       </c>
@@ -24317,7 +24317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>529</v>
       </c>
@@ -24379,7 +24379,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>529</v>
       </c>
@@ -24441,7 +24441,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>529</v>
       </c>
@@ -24503,7 +24503,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>529</v>
       </c>
@@ -24565,7 +24565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>529</v>
       </c>
@@ -24627,7 +24627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>529</v>
       </c>
@@ -24689,7 +24689,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>529</v>
       </c>
@@ -24751,7 +24751,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>529</v>
       </c>
@@ -24813,7 +24813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>529</v>
       </c>
@@ -24875,7 +24875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>529</v>
       </c>
@@ -24937,7 +24937,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>529</v>
       </c>
@@ -24999,7 +24999,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>529</v>
       </c>
@@ -25061,7 +25061,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>529</v>
       </c>
@@ -25123,7 +25123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>529</v>
       </c>
@@ -25185,7 +25185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>529</v>
       </c>
@@ -25247,7 +25247,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>529</v>
       </c>
@@ -25309,7 +25309,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>529</v>
       </c>
@@ -25371,7 +25371,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>529</v>
       </c>
@@ -25433,7 +25433,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>529</v>
       </c>
@@ -25495,7 +25495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>529</v>
       </c>
@@ -25557,7 +25557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>529</v>
       </c>
@@ -25619,7 +25619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>529</v>
       </c>
@@ -25681,7 +25681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>529</v>
       </c>
@@ -25743,7 +25743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>529</v>
       </c>
@@ -25805,7 +25805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>529</v>
       </c>
@@ -25867,7 +25867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>529</v>
       </c>
@@ -25929,7 +25929,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>529</v>
       </c>
@@ -25991,7 +25991,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>529</v>
       </c>
@@ -26053,7 +26053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>529</v>
       </c>
@@ -26115,7 +26115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>529</v>
       </c>
@@ -26177,7 +26177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>529</v>
       </c>
@@ -26239,7 +26239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>529</v>
       </c>
@@ -26301,7 +26301,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>529</v>
       </c>
@@ -26363,7 +26363,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>529</v>
       </c>
@@ -26425,7 +26425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>529</v>
       </c>
@@ -26487,7 +26487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>529</v>
       </c>
@@ -26549,7 +26549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>529</v>
       </c>
@@ -26611,7 +26611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>529</v>
       </c>
@@ -26673,7 +26673,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>529</v>
       </c>
@@ -26735,7 +26735,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>529</v>
       </c>
@@ -26797,7 +26797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>529</v>
       </c>
@@ -26859,7 +26859,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>529</v>
       </c>
@@ -26921,7 +26921,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>529</v>
       </c>
@@ -26983,7 +26983,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>529</v>
       </c>
@@ -27045,7 +27045,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>529</v>
       </c>
@@ -27107,7 +27107,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>529</v>
       </c>
@@ -27169,7 +27169,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>529</v>
       </c>
@@ -27231,7 +27231,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>529</v>
       </c>
@@ -27293,7 +27293,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>529</v>
       </c>
@@ -27355,7 +27355,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>529</v>
       </c>
@@ -27417,7 +27417,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>529</v>
       </c>
@@ -27479,7 +27479,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>529</v>
       </c>
@@ -27541,7 +27541,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>529</v>
       </c>
@@ -27603,7 +27603,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>529</v>
       </c>
@@ -27665,7 +27665,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>529</v>
       </c>
@@ -27727,7 +27727,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>529</v>
       </c>
@@ -27789,7 +27789,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>529</v>
       </c>
@@ -27851,7 +27851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>529</v>
       </c>
@@ -27913,7 +27913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>529</v>
       </c>
@@ -27975,7 +27975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>529</v>
       </c>
@@ -28037,7 +28037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>529</v>
       </c>
@@ -28099,7 +28099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>529</v>
       </c>
@@ -28161,7 +28161,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>529</v>
       </c>
@@ -28223,7 +28223,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>529</v>
       </c>
@@ -28285,7 +28285,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>529</v>
       </c>
@@ -28347,7 +28347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>529</v>
       </c>
@@ -28409,7 +28409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>529</v>
       </c>
@@ -28471,7 +28471,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>529</v>
       </c>
@@ -28533,7 +28533,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>529</v>
       </c>
@@ -28595,7 +28595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>529</v>
       </c>
@@ -28657,7 +28657,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>529</v>
       </c>
@@ -28719,7 +28719,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>529</v>
       </c>
@@ -28781,7 +28781,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>529</v>
       </c>
@@ -28843,7 +28843,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>529</v>
       </c>
@@ -28905,7 +28905,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>529</v>
       </c>
@@ -28967,7 +28967,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>529</v>
       </c>
@@ -29029,7 +29029,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>529</v>
       </c>
@@ -29091,7 +29091,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>529</v>
       </c>
@@ -29153,7 +29153,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>529</v>
       </c>
@@ -29215,7 +29215,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>529</v>
       </c>
@@ -29277,7 +29277,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>529</v>
       </c>
@@ -29339,7 +29339,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>529</v>
       </c>
@@ -29401,7 +29401,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>529</v>
       </c>
@@ -29463,7 +29463,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>529</v>
       </c>
@@ -29525,7 +29525,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>529</v>
       </c>
@@ -29587,7 +29587,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>529</v>
       </c>
@@ -29649,7 +29649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>529</v>
       </c>
@@ -29711,7 +29711,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>529</v>
       </c>
@@ -29773,7 +29773,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>529</v>
       </c>
@@ -29835,7 +29835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>529</v>
       </c>
@@ -29897,7 +29897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>529</v>
       </c>
@@ -29959,7 +29959,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>529</v>
       </c>
@@ -30021,7 +30021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>529</v>
       </c>
@@ -30083,7 +30083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>529</v>
       </c>
@@ -30145,7 +30145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>529</v>
       </c>
@@ -30207,7 +30207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>529</v>
       </c>
@@ -30269,7 +30269,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>529</v>
       </c>
@@ -30331,7 +30331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>529</v>
       </c>
@@ -30393,7 +30393,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>529</v>
       </c>
@@ -30455,7 +30455,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>529</v>
       </c>
@@ -30517,7 +30517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>529</v>
       </c>
@@ -30579,7 +30579,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>529</v>
       </c>
@@ -30641,7 +30641,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>529</v>
       </c>
@@ -30703,7 +30703,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>529</v>
       </c>
@@ -30765,7 +30765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>529</v>
       </c>
@@ -30827,7 +30827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>529</v>
       </c>
@@ -30889,7 +30889,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>529</v>
       </c>
@@ -30951,7 +30951,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>529</v>
       </c>
@@ -31013,7 +31013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="262" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A262" s="8" t="s">
         <v>529</v>
       </c>
@@ -31075,7 +31075,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>529</v>
       </c>
@@ -31137,7 +31137,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>529</v>
       </c>
@@ -31199,7 +31199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>529</v>
       </c>
@@ -31261,7 +31261,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>529</v>
       </c>
@@ -31323,7 +31323,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>529</v>
       </c>
@@ -31385,7 +31385,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>529</v>
       </c>
@@ -31447,7 +31447,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>529</v>
       </c>
@@ -31509,7 +31509,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>529</v>
       </c>
@@ -31571,7 +31571,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>529</v>
       </c>
@@ -31633,7 +31633,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>529</v>
       </c>
@@ -31695,7 +31695,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>529</v>
       </c>
@@ -31757,7 +31757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>529</v>
       </c>
@@ -31819,7 +31819,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>529</v>
       </c>
@@ -31881,7 +31881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>529</v>
       </c>
@@ -31943,7 +31943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>529</v>
       </c>
@@ -32005,7 +32005,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>529</v>
       </c>
@@ -32067,7 +32067,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>529</v>
       </c>
@@ -32129,7 +32129,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>529</v>
       </c>
@@ -32191,7 +32191,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>529</v>
       </c>
@@ -32253,7 +32253,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>529</v>
       </c>
@@ -32315,7 +32315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>529</v>
       </c>
@@ -32377,7 +32377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="284" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A284" s="8" t="s">
         <v>529</v>
       </c>
@@ -32439,7 +32439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>529</v>
       </c>
@@ -32501,7 +32501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>529</v>
       </c>
@@ -32563,7 +32563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>529</v>
       </c>
@@ -32625,7 +32625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>529</v>
       </c>
@@ -32687,7 +32687,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>529</v>
       </c>
@@ -32749,7 +32749,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>529</v>
       </c>
@@ -32811,7 +32811,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>529</v>
       </c>
@@ -32873,7 +32873,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>529</v>
       </c>
@@ -32935,7 +32935,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>529</v>
       </c>
@@ -32997,7 +32997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>529</v>
       </c>
@@ -33059,7 +33059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>529</v>
       </c>
@@ -33121,7 +33121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>529</v>
       </c>
@@ -33183,7 +33183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>529</v>
       </c>
@@ -33245,7 +33245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>529</v>
       </c>
@@ -33307,7 +33307,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>529</v>
       </c>
@@ -33369,7 +33369,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>529</v>
       </c>
@@ -33431,7 +33431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>529</v>
       </c>
@@ -33493,7 +33493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>529</v>
       </c>
@@ -33555,7 +33555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>529</v>
       </c>
@@ -33617,7 +33617,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>529</v>
       </c>
@@ -33679,7 +33679,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>529</v>
       </c>
@@ -33741,7 +33741,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>529</v>
       </c>
@@ -33803,7 +33803,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>529</v>
       </c>
@@ -33865,7 +33865,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>529</v>
       </c>
@@ -33927,7 +33927,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>529</v>
       </c>
@@ -33989,7 +33989,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>529</v>
       </c>
@@ -34051,7 +34051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>529</v>
       </c>
@@ -34113,7 +34113,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>529</v>
       </c>
@@ -34175,7 +34175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>529</v>
       </c>
@@ -34237,7 +34237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>529</v>
       </c>
@@ -34299,7 +34299,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>529</v>
       </c>
@@ -34361,7 +34361,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>529</v>
       </c>
@@ -34423,7 +34423,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>529</v>
       </c>
@@ -34485,7 +34485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>529</v>
       </c>
@@ -34547,7 +34547,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>529</v>
       </c>
@@ -34609,7 +34609,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>529</v>
       </c>
@@ -34671,7 +34671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>529</v>
       </c>
@@ -34733,7 +34733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>529</v>
       </c>
@@ -34795,7 +34795,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>529</v>
       </c>
@@ -34857,7 +34857,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>529</v>
       </c>
@@ -34919,7 +34919,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>529</v>
       </c>
@@ -34981,7 +34981,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>529</v>
       </c>
@@ -35043,7 +35043,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>529</v>
       </c>
@@ -35105,7 +35105,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>529</v>
       </c>
@@ -35167,7 +35167,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>529</v>
       </c>
@@ -35229,7 +35229,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>529</v>
       </c>
@@ -35291,7 +35291,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>529</v>
       </c>
@@ -35353,7 +35353,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>529</v>
       </c>
@@ -35415,7 +35415,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>529</v>
       </c>
@@ -35477,7 +35477,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>529</v>
       </c>
@@ -35539,7 +35539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>529</v>
       </c>
@@ -35601,7 +35601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>529</v>
       </c>
@@ -35663,7 +35663,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>529</v>
       </c>
@@ -35725,7 +35725,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>529</v>
       </c>
@@ -35787,7 +35787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>529</v>
       </c>
@@ -35849,7 +35849,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>529</v>
       </c>
@@ -35911,7 +35911,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>529</v>
       </c>
@@ -35973,7 +35973,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>529</v>
       </c>
@@ -36035,7 +36035,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>529</v>
       </c>
@@ -36097,7 +36097,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>529</v>
       </c>
@@ -36159,7 +36159,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="345" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>529</v>
       </c>
@@ -36221,7 +36221,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>529</v>
       </c>
@@ -36283,7 +36283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>529</v>
       </c>
@@ -36345,7 +36345,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>529</v>
       </c>
@@ -36407,7 +36407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>529</v>
       </c>
@@ -36469,7 +36469,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>529</v>
       </c>
@@ -36531,7 +36531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>529</v>
       </c>
@@ -36593,7 +36593,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>529</v>
       </c>
@@ -36655,7 +36655,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>529</v>
       </c>
@@ -36717,7 +36717,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>529</v>
       </c>
@@ -36779,7 +36779,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>529</v>
       </c>
@@ -36841,7 +36841,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>529</v>
       </c>
@@ -36903,7 +36903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>529</v>
       </c>
@@ -36965,7 +36965,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>529</v>
       </c>
@@ -37027,7 +37027,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>529</v>
       </c>
@@ -37089,7 +37089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>529</v>
       </c>
@@ -37151,7 +37151,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>529</v>
       </c>
@@ -37213,7 +37213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>529</v>
       </c>
@@ -37275,7 +37275,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>529</v>
       </c>
@@ -37337,7 +37337,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>529</v>
       </c>
@@ -37399,7 +37399,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>529</v>
       </c>
@@ -37461,7 +37461,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>529</v>
       </c>
@@ -37523,7 +37523,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>529</v>
       </c>
@@ -37585,7 +37585,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>529</v>
       </c>
@@ -37647,7 +37647,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>529</v>
       </c>
@@ -37709,7 +37709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>529</v>
       </c>
@@ -37771,7 +37771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>529</v>
       </c>
@@ -37833,7 +37833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>529</v>
       </c>
@@ -37895,7 +37895,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>529</v>
       </c>
@@ -37957,7 +37957,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>529</v>
       </c>
@@ -38019,7 +38019,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>529</v>
       </c>
@@ -38081,7 +38081,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>529</v>
       </c>
@@ -38143,7 +38143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>529</v>
       </c>
@@ -38205,7 +38205,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>529</v>
       </c>
@@ -38267,7 +38267,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>529</v>
       </c>
@@ -38329,7 +38329,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="380" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>529</v>
       </c>
@@ -38391,7 +38391,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="381" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>529</v>
       </c>
@@ -38453,7 +38453,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="382" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>529</v>
       </c>
@@ -38515,7 +38515,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>529</v>
       </c>
@@ -38577,7 +38577,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>529</v>
       </c>
@@ -38639,7 +38639,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>529</v>
       </c>
@@ -38701,7 +38701,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>529</v>
       </c>
@@ -38763,7 +38763,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>529</v>
       </c>
@@ -38825,7 +38825,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>529</v>
       </c>
@@ -38887,7 +38887,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>529</v>
       </c>
@@ -38949,7 +38949,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>529</v>
       </c>
@@ -39011,7 +39011,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="391" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>529</v>
       </c>
@@ -39073,7 +39073,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>529</v>
       </c>
@@ -39135,7 +39135,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>529</v>
       </c>
@@ -39197,7 +39197,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>529</v>
       </c>
@@ -39259,7 +39259,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>529</v>
       </c>
@@ -39321,7 +39321,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="396" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>529</v>
       </c>
@@ -39383,7 +39383,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="397" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>529</v>
       </c>
@@ -39445,7 +39445,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>529</v>
       </c>
@@ -39507,7 +39507,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>529</v>
       </c>
@@ -39569,7 +39569,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>529</v>
       </c>
@@ -39631,7 +39631,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="401" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>529</v>
       </c>
@@ -39693,7 +39693,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="402" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>529</v>
       </c>
@@ -39755,7 +39755,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="403" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>529</v>
       </c>
@@ -39817,7 +39817,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="404" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>529</v>
       </c>
@@ -39879,7 +39879,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="405" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>529</v>
       </c>
@@ -39941,7 +39941,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="406" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>529</v>
       </c>
@@ -40003,7 +40003,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="407" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>529</v>
       </c>
@@ -40065,7 +40065,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="408" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>529</v>
       </c>
@@ -40127,7 +40127,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="409" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>529</v>
       </c>
@@ -40189,7 +40189,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="410" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>529</v>
       </c>
@@ -40251,7 +40251,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="411" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>529</v>
       </c>
@@ -40313,7 +40313,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="412" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>529</v>
       </c>
@@ -40375,7 +40375,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="413" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>529</v>
       </c>
@@ -40437,7 +40437,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="414" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>529</v>
       </c>
@@ -40499,7 +40499,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="415" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>529</v>
       </c>
@@ -40561,7 +40561,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="416" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>529</v>
       </c>
@@ -40623,7 +40623,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="417" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>529</v>
       </c>
@@ -40685,7 +40685,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="418" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>529</v>
       </c>
@@ -40747,7 +40747,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="419" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>529</v>
       </c>
@@ -40809,7 +40809,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="420" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>529</v>
       </c>
@@ -40871,7 +40871,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="421" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>529</v>
       </c>
@@ -40933,7 +40933,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="422" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>529</v>
       </c>
@@ -40995,7 +40995,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="423" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>529</v>
       </c>
@@ -41057,7 +41057,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="424" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>529</v>
       </c>
@@ -41119,7 +41119,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="425" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>529</v>
       </c>
@@ -41181,7 +41181,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="426" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>529</v>
       </c>
@@ -41243,7 +41243,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="427" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>529</v>
       </c>
@@ -41305,7 +41305,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="428" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>529</v>
       </c>
@@ -41367,7 +41367,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="429" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A429" s="8" t="s">
         <v>529</v>
       </c>
@@ -41429,7 +41429,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="430" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>529</v>
       </c>
@@ -41491,7 +41491,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="431" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>529</v>
       </c>
@@ -41553,7 +41553,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="432" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>529</v>
       </c>
@@ -41615,7 +41615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="433" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>529</v>
       </c>
@@ -41677,7 +41677,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="434" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>529</v>
       </c>
@@ -41739,7 +41739,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="435" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>529</v>
       </c>
@@ -41801,7 +41801,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="436" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>529</v>
       </c>
@@ -41863,7 +41863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="437" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>529</v>
       </c>
@@ -41925,7 +41925,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="438" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>529</v>
       </c>
@@ -41987,7 +41987,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="439" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>529</v>
       </c>
@@ -42049,7 +42049,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="440" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>529</v>
       </c>
@@ -42111,7 +42111,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="441" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>529</v>
       </c>
@@ -42173,7 +42173,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="442" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>529</v>
       </c>
@@ -42235,7 +42235,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="443" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>529</v>
       </c>
@@ -42297,7 +42297,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="444" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>529</v>
       </c>
@@ -42359,7 +42359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="445" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>529</v>
       </c>
@@ -42421,7 +42421,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="446" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>529</v>
       </c>
@@ -42483,7 +42483,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="447" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>529</v>
       </c>
@@ -42545,7 +42545,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="448" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>529</v>
       </c>
@@ -42607,7 +42607,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="449" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>529</v>
       </c>
@@ -42669,7 +42669,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="450" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>529</v>
       </c>
@@ -42731,7 +42731,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="451" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>529</v>
       </c>
@@ -42793,7 +42793,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="452" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>529</v>
       </c>
@@ -42855,7 +42855,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="453" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>529</v>
       </c>
@@ -42917,7 +42917,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="454" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>529</v>
       </c>
@@ -42979,7 +42979,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="455" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>529</v>
       </c>
@@ -43041,7 +43041,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="456" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>529</v>
       </c>
@@ -43103,7 +43103,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="457" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>529</v>
       </c>
@@ -43165,7 +43165,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="458" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>529</v>
       </c>
@@ -43227,7 +43227,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="459" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>529</v>
       </c>
@@ -43289,7 +43289,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="460" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>529</v>
       </c>
@@ -43351,7 +43351,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="461" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>529</v>
       </c>
@@ -43413,7 +43413,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="462" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>529</v>
       </c>
@@ -43475,7 +43475,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="463" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>529</v>
       </c>
@@ -43537,7 +43537,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="464" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>529</v>
       </c>
@@ -43599,7 +43599,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="465" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>529</v>
       </c>
@@ -43661,7 +43661,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>529</v>
       </c>
@@ -43723,7 +43723,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>529</v>
       </c>
@@ -43785,7 +43785,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>529</v>
       </c>
@@ -43847,7 +43847,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>529</v>
       </c>
@@ -43909,7 +43909,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>529</v>
       </c>
@@ -43971,7 +43971,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>529</v>
       </c>
@@ -44033,7 +44033,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="472" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>529</v>
       </c>
@@ -44095,7 +44095,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="473" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>529</v>
       </c>
@@ -44157,7 +44157,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>529</v>
       </c>
@@ -44219,7 +44219,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>529</v>
       </c>
@@ -44281,7 +44281,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>529</v>
       </c>
@@ -44343,7 +44343,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="477" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>529</v>
       </c>
@@ -44405,7 +44405,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>529</v>
       </c>
@@ -44467,7 +44467,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="479" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>529</v>
       </c>
@@ -44529,7 +44529,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>529</v>
       </c>
@@ -44591,7 +44591,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="481" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>529</v>
       </c>
@@ -44653,7 +44653,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="482" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>529</v>
       </c>
@@ -44715,7 +44715,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="483" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>529</v>
       </c>
@@ -44777,7 +44777,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="484" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>529</v>
       </c>
@@ -44839,7 +44839,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="485" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>529</v>
       </c>
@@ -44901,7 +44901,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="486" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>529</v>
       </c>
@@ -44963,7 +44963,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="487" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>529</v>
       </c>
@@ -45025,7 +45025,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="488" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>529</v>
       </c>
@@ -45087,7 +45087,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="489" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>529</v>
       </c>
@@ -45149,7 +45149,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="490" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>529</v>
       </c>
@@ -45211,7 +45211,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="491" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>529</v>
       </c>
@@ -45273,7 +45273,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="492" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>529</v>
       </c>
@@ -45335,7 +45335,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="493" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>529</v>
       </c>
@@ -45397,7 +45397,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>529</v>
       </c>
@@ -45459,7 +45459,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>529</v>
       </c>
@@ -45521,7 +45521,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>529</v>
       </c>
@@ -45583,7 +45583,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="497" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>529</v>
       </c>
@@ -45645,7 +45645,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="498" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>529</v>
       </c>
@@ -45707,7 +45707,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="499" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>529</v>
       </c>
@@ -45769,7 +45769,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="500" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>529</v>
       </c>
@@ -45831,7 +45831,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="501" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>529</v>
       </c>
@@ -45893,7 +45893,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="502" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>529</v>
       </c>
@@ -45955,7 +45955,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="503" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>529</v>
       </c>
@@ -46017,7 +46017,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="504" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>529</v>
       </c>
@@ -46079,7 +46079,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="505" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>529</v>
       </c>
@@ -46141,7 +46141,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="506" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>529</v>
       </c>
@@ -46203,7 +46203,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="507" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>529</v>
       </c>
@@ -46265,7 +46265,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="508" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>529</v>
       </c>
@@ -46327,7 +46327,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="509" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>529</v>
       </c>
@@ -46389,7 +46389,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="510" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>529</v>
       </c>
@@ -46451,7 +46451,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="511" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>529</v>
       </c>
@@ -46513,7 +46513,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="512" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>529</v>
       </c>
@@ -46575,7 +46575,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="513" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>529</v>
       </c>
@@ -46637,7 +46637,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="514" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>529</v>
       </c>
@@ -46699,7 +46699,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="515" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>529</v>
       </c>
@@ -46761,7 +46761,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="516" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>529</v>
       </c>
@@ -46823,7 +46823,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="517" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>529</v>
       </c>
@@ -46885,7 +46885,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="518" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>529</v>
       </c>
@@ -46947,7 +46947,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="519" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>529</v>
       </c>
@@ -47009,7 +47009,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="520" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>529</v>
       </c>
@@ -47071,7 +47071,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="521" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>529</v>
       </c>
@@ -47133,7 +47133,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="522" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>529</v>
       </c>
@@ -47195,7 +47195,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="523" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>529</v>
       </c>
@@ -47257,7 +47257,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="524" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>529</v>
       </c>
@@ -47319,7 +47319,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="525" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>529</v>
       </c>
@@ -47381,7 +47381,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="526" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>529</v>
       </c>
@@ -47443,7 +47443,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="527" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>529</v>
       </c>
@@ -47505,7 +47505,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="528" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>529</v>
       </c>
@@ -47567,7 +47567,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="529" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>529</v>
       </c>
@@ -47629,7 +47629,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="530" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>529</v>
       </c>
@@ -47691,7 +47691,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="531" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>529</v>
       </c>
@@ -47753,7 +47753,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="532" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>529</v>
       </c>
@@ -47815,7 +47815,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="533" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>529</v>
       </c>
@@ -47877,7 +47877,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="534" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>529</v>
       </c>
@@ -47939,7 +47939,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="535" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>529</v>
       </c>
@@ -48001,7 +48001,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="536" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>529</v>
       </c>
@@ -48063,7 +48063,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="537" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>529</v>
       </c>
@@ -48125,7 +48125,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="538" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>529</v>
       </c>
@@ -48187,7 +48187,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="539" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>529</v>
       </c>
@@ -48249,7 +48249,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="540" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>529</v>
       </c>
@@ -48311,7 +48311,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="541" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>529</v>
       </c>
@@ -48373,7 +48373,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="542" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>529</v>
       </c>
@@ -48435,7 +48435,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="543" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>529</v>
       </c>
@@ -48497,7 +48497,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="544" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>529</v>
       </c>
@@ -48559,7 +48559,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="545" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>529</v>
       </c>
@@ -48621,7 +48621,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="546" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>529</v>
       </c>
@@ -48683,7 +48683,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="547" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>529</v>
       </c>
@@ -48745,7 +48745,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="548" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>529</v>
       </c>
@@ -48807,7 +48807,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="549" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>529</v>
       </c>
@@ -48869,7 +48869,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="550" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>529</v>
       </c>
@@ -48931,7 +48931,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="551" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>529</v>
       </c>
@@ -48993,7 +48993,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="552" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>529</v>
       </c>
@@ -49055,7 +49055,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="553" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>529</v>
       </c>
@@ -49117,7 +49117,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="554" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>529</v>
       </c>
@@ -49179,7 +49179,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="555" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>529</v>
       </c>
@@ -49241,7 +49241,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="556" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>529</v>
       </c>
@@ -49303,7 +49303,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="557" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>529</v>
       </c>
@@ -49365,7 +49365,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="558" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>529</v>
       </c>
@@ -49427,7 +49427,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="559" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>529</v>
       </c>
@@ -49489,7 +49489,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="560" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>529</v>
       </c>
@@ -49551,7 +49551,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="561" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>529</v>
       </c>
@@ -49613,7 +49613,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="562" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>529</v>
       </c>
@@ -49675,7 +49675,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="563" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>529</v>
       </c>
@@ -49737,7 +49737,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="564" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>529</v>
       </c>
@@ -49799,7 +49799,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="565" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>529</v>
       </c>
@@ -49861,7 +49861,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="566" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>529</v>
       </c>
@@ -49923,7 +49923,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="567" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>529</v>
       </c>
@@ -49985,7 +49985,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="568" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>529</v>
       </c>
@@ -50047,7 +50047,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="569" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>529</v>
       </c>
@@ -50109,7 +50109,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="570" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>529</v>
       </c>
@@ -50171,7 +50171,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="571" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>529</v>
       </c>
@@ -50233,7 +50233,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="572" spans="1:20" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:20" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>529</v>
       </c>
@@ -50295,7 +50295,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="573" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>529</v>
       </c>
@@ -50357,7 +50357,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="574" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>529</v>
       </c>
@@ -50419,7 +50419,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="575" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>529</v>
       </c>
@@ -50481,7 +50481,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="576" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>529</v>
       </c>
@@ -50543,7 +50543,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="577" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>529</v>
       </c>
@@ -50605,7 +50605,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="578" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>529</v>
       </c>
@@ -50667,7 +50667,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="579" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>529</v>
       </c>
@@ -50729,7 +50729,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="580" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>529</v>
       </c>
@@ -50791,7 +50791,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="581" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>529</v>
       </c>
@@ -50853,7 +50853,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="582" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>529</v>
       </c>
@@ -50915,7 +50915,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="583" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>529</v>
       </c>
@@ -50977,7 +50977,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="584" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>529</v>
       </c>
@@ -51039,7 +51039,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="585" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>529</v>
       </c>
@@ -51101,7 +51101,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="586" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>529</v>
       </c>
@@ -51163,7 +51163,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="587" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>529</v>
       </c>
@@ -51225,7 +51225,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="588" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>529</v>
       </c>
@@ -51287,7 +51287,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="589" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>529</v>
       </c>
@@ -51349,7 +51349,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="590" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>529</v>
       </c>
@@ -51411,7 +51411,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="591" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>529</v>
       </c>
@@ -51473,7 +51473,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="592" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>529</v>
       </c>
@@ -51535,7 +51535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="593" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A593" s="6" t="s">
         <v>529</v>
       </c>
@@ -51597,7 +51597,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="594" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A594" s="6" t="s">
         <v>529</v>
       </c>
@@ -51659,7 +51659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="595" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>529</v>
       </c>
@@ -51721,7 +51721,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="596" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>529</v>
       </c>
@@ -51783,7 +51783,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="597" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>529</v>
       </c>
@@ -51845,7 +51845,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="598" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>529</v>
       </c>
@@ -51907,7 +51907,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="599" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>529</v>
       </c>
@@ -51966,6 +51966,192 @@
         <v>1</v>
       </c>
       <c r="T599" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A600" t="s">
+        <v>529</v>
+      </c>
+      <c r="B600" t="s">
+        <v>530</v>
+      </c>
+      <c r="C600" t="s">
+        <v>531</v>
+      </c>
+      <c r="D600" t="s">
+        <v>532</v>
+      </c>
+      <c r="E600" t="s">
+        <v>533</v>
+      </c>
+      <c r="F600" t="s">
+        <v>534</v>
+      </c>
+      <c r="G600" t="s">
+        <v>12</v>
+      </c>
+      <c r="H600" t="s">
+        <v>67</v>
+      </c>
+      <c r="I600" t="s">
+        <v>68</v>
+      </c>
+      <c r="J600" s="12">
+        <v>6121361</v>
+      </c>
+      <c r="K600" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="L600" t="s">
+        <v>531</v>
+      </c>
+      <c r="M600" s="12">
+        <v>6121361</v>
+      </c>
+      <c r="N600" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="O600" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="P600" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q600" t="s">
+        <v>536</v>
+      </c>
+      <c r="R600" t="s">
+        <v>536</v>
+      </c>
+      <c r="S600" s="2">
+        <v>1</v>
+      </c>
+      <c r="T600" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A601" t="s">
+        <v>529</v>
+      </c>
+      <c r="B601" t="s">
+        <v>530</v>
+      </c>
+      <c r="C601" t="s">
+        <v>531</v>
+      </c>
+      <c r="D601" t="s">
+        <v>532</v>
+      </c>
+      <c r="E601" t="s">
+        <v>533</v>
+      </c>
+      <c r="F601" t="s">
+        <v>534</v>
+      </c>
+      <c r="G601" t="s">
+        <v>12</v>
+      </c>
+      <c r="H601" t="s">
+        <v>67</v>
+      </c>
+      <c r="I601" t="s">
+        <v>68</v>
+      </c>
+      <c r="J601" s="12">
+        <v>6120401</v>
+      </c>
+      <c r="K601" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="L601" t="s">
+        <v>531</v>
+      </c>
+      <c r="M601" s="12">
+        <v>6120401</v>
+      </c>
+      <c r="N601" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="O601" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="P601" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q601" t="s">
+        <v>536</v>
+      </c>
+      <c r="R601" t="s">
+        <v>536</v>
+      </c>
+      <c r="S601" s="2">
+        <v>1</v>
+      </c>
+      <c r="T601" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A602" t="s">
+        <v>529</v>
+      </c>
+      <c r="B602" t="s">
+        <v>530</v>
+      </c>
+      <c r="C602" t="s">
+        <v>531</v>
+      </c>
+      <c r="D602" t="s">
+        <v>532</v>
+      </c>
+      <c r="E602" t="s">
+        <v>533</v>
+      </c>
+      <c r="F602" t="s">
+        <v>534</v>
+      </c>
+      <c r="G602" t="s">
+        <v>12</v>
+      </c>
+      <c r="H602" t="s">
+        <v>67</v>
+      </c>
+      <c r="I602" t="s">
+        <v>68</v>
+      </c>
+      <c r="J602" s="12">
+        <v>6120300</v>
+      </c>
+      <c r="K602" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="L602" t="s">
+        <v>531</v>
+      </c>
+      <c r="M602" s="12">
+        <v>6120300</v>
+      </c>
+      <c r="N602" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="O602" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="P602" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q602" t="s">
+        <v>536</v>
+      </c>
+      <c r="R602" t="s">
+        <v>536</v>
+      </c>
+      <c r="S602" s="2">
+        <v>1</v>
+      </c>
+      <c r="T602" s="2">
         <v>1</v>
       </c>
     </row>
